--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdPartnerInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdPartnerInfo001.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhouqiang\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\IdeaProject2019\nanyin\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2624CFC8-E39D-4DE3-937E-49007C18D77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB57AA7B-0087-40F2-8ACA-83EC95FBB521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,27 +100,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -129,24 +114,30 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -488,16 +479,16 @@
   <dimension ref="A1:L28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.1328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="29.265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="24.265625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="27.46484375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="28.46484375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="21.3984375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="22.46484375" style="5" customWidth="1"/>
-    <col min="8" max="8" width="22.59765625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="15.1328125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="16.46484375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="16.1328125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="29.265625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="24.265625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="27.46484375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="28.46484375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="21.3984375" style="8" customWidth="1"/>
+    <col min="7" max="7" width="22.46484375" style="8" customWidth="1"/>
+    <col min="8" max="8" width="22.59765625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="15.1328125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="16.46484375" style="2" customWidth="1"/>
     <col min="257" max="257" width="16.1328125" customWidth="1"/>
     <col min="258" max="258" width="29.265625" customWidth="1"/>
     <col min="259" max="259" width="24.265625" customWidth="1"/>
@@ -1131,151 +1122,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="L4" s="1"/>
+      <c r="L4" s="10"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-    </row>
-    <row r="22" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-    </row>
-    <row r="23" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-    </row>
-    <row r="28" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="K28" s="1"/>
+    <row r="28" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K28" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdPartnerInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdPartnerInfo001.xlsx
@@ -29,10 +29,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>产品名称</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>合作机构</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -50,6 +46,10 @@
   </si>
   <si>
     <t>更新人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品全称</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1097,22 +1097,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>7</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdPartnerInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdPartnerInfo001.xlsx
@@ -29,10 +29,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>合作机构</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>生效日</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -50,6 +46,10 @@
   </si>
   <si>
     <t>产品全称</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>合作机构（机构名称以“、”隔开）</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -450,7 +450,7 @@
     <col min="1" max="1" width="16.125" style="3" customWidth="1"/>
     <col min="2" max="2" width="29.25" style="3" customWidth="1"/>
     <col min="3" max="3" width="24.25" style="3" customWidth="1"/>
-    <col min="4" max="4" width="27.5" style="6" customWidth="1"/>
+    <col min="4" max="4" width="29.625" style="6" customWidth="1"/>
     <col min="5" max="5" width="28.5" style="11" customWidth="1"/>
     <col min="6" max="6" width="21.375" style="11" customWidth="1"/>
     <col min="7" max="7" width="22.5" style="8" customWidth="1"/>
@@ -1097,22 +1097,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
